--- a/data/Base de Datos Scopus.xlsx
+++ b/data/Base de Datos Scopus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tecnoutb-my.sharepoint.com/personal/jualtamar_utb_edu_co/Documents/Juan Pablo/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gsus\Desktop\Prog\Git\Scopus-Metrics-Utb\Scopus-Metrics-UTBt\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ABC74B2-BAC5-467E-A8DA-5FF1BDFA3FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84BCCEC4-34C4-4A06-BA44-AE9242883D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{AF2084BB-61DF-4DBF-8840-FC3C0AFA8DDF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AF2084BB-61DF-4DBF-8840-FC3C0AFA8DDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -1523,16 +1523,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F5F268-D7A4-4415-8F1B-CD4813DE100D}">
   <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.90625" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="79.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="79.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>34</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>35</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>36</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>37</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>40</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>41</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>42</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>43</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>44</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>45</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>46</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>47</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>48</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>49</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>50</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>51</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>52</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>53</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>54</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>55</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>56</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>57</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>58</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>59</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>60</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>61</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>62</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>63</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>64</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>65</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>66</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>67</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>68</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>69</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>70</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>71</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>72</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>73</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>74</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>75</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
         <v>76</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
         <v>77</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
         <v>78</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>79</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>80</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>81</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>82</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
         <v>83</v>
       </c>
